--- a/data/training.xlsx
+++ b/data/training.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BFCE8F-5463-45C8-A983-63BD360B14FF}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48869439-7182-4A70-95AA-D4CBFAE638CF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -104,6 +104,15 @@
   </si>
   <si>
     <t>https://psiweb.org/vod/item/ewig-webinar-applying-the-estimand-framework-to-clinical-pharmacology-trials-with-a-case-study-in-bioequivalance</t>
+  </si>
+  <si>
+    <t>https://www.psiweb.org/vod/item/enhancing-clinical-study-reporting-with-the-estimand-framework</t>
+  </si>
+  <si>
+    <t>21 April 2026</t>
+  </si>
+  <si>
+    <t>Enhancing Clinical Study Reporting with the Estimand Framework</t>
   </si>
 </sst>
 </file>
@@ -175,10 +184,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
@@ -551,14 +556,26 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{38AF4AE0-58AB-4C8B-91BE-2EE131DE8F7E}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{B1075240-DEAA-4C9D-B996-BB474F2FDFF9}"/>
     <hyperlink ref="D7" r:id="rId3" display="https://emea01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.youtube.com%2Fwatch%3Fv%3DzfgeKWvXwn0&amp;data=05%7C02%7C%7C1e07f046180141b0ed5708de073f6688%7C84df9e7fe9f640afb435aaaaaaaaaaaa%7C1%7C0%7C638956166036706617%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=4PNdCVfvIymh3OMre0PiE3omxYuaUJ0M0Z0KaV8JJQo%3D&amp;reserved=0" xr:uid="{A807C07B-804D-4C49-84A3-C8F456FD98BD}"/>
     <hyperlink ref="C7" r:id="rId4" xr:uid="{A62B021E-0ED0-46EB-9169-28783ACD5A91}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{D9A1F525-58F4-422D-AF95-9646FCC88706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data/training.xlsx
+++ b/data/training.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48869439-7182-4A70-95AA-D4CBFAE638CF}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90306BBA-D702-4024-B19D-0808A4FC4152}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>Enhancing Clinical Study Reporting with the Estimand Framework</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7NNDEytTm-Y</t>
   </si>
 </sst>
 </file>
@@ -184,6 +187,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,6 +573,9 @@
       <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
